--- a/data/nzd0037/nzd0037.xlsx
+++ b/data/nzd0037/nzd0037.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N501"/>
+  <dimension ref="A1:N507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24498,6 +24498,294 @@
         <v>356.47</v>
       </c>
       <c r="N501" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>353.72</v>
+      </c>
+      <c r="C502" t="n">
+        <v>347.72</v>
+      </c>
+      <c r="D502" t="n">
+        <v>344.99</v>
+      </c>
+      <c r="E502" t="n">
+        <v>338.77</v>
+      </c>
+      <c r="F502" t="n">
+        <v>324.56</v>
+      </c>
+      <c r="G502" t="n">
+        <v>331.01</v>
+      </c>
+      <c r="H502" t="n">
+        <v>347.57</v>
+      </c>
+      <c r="I502" t="n">
+        <v>367.07</v>
+      </c>
+      <c r="J502" t="n">
+        <v>372.59</v>
+      </c>
+      <c r="K502" t="n">
+        <v>333.17</v>
+      </c>
+      <c r="L502" t="n">
+        <v>349.3</v>
+      </c>
+      <c r="M502" t="n">
+        <v>355.71</v>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>354.17</v>
+      </c>
+      <c r="C503" t="n">
+        <v>348.67</v>
+      </c>
+      <c r="D503" t="n">
+        <v>345.42</v>
+      </c>
+      <c r="E503" t="n">
+        <v>339.45</v>
+      </c>
+      <c r="F503" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="G503" t="n">
+        <v>332.25</v>
+      </c>
+      <c r="H503" t="n">
+        <v>348.79</v>
+      </c>
+      <c r="I503" t="n">
+        <v>365.96</v>
+      </c>
+      <c r="J503" t="n">
+        <v>372.26</v>
+      </c>
+      <c r="K503" t="n">
+        <v>333.77</v>
+      </c>
+      <c r="L503" t="n">
+        <v>349.68</v>
+      </c>
+      <c r="M503" t="n">
+        <v>356.09</v>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>352.74</v>
+      </c>
+      <c r="C504" t="n">
+        <v>347.41</v>
+      </c>
+      <c r="D504" t="n">
+        <v>345.88</v>
+      </c>
+      <c r="E504" t="n">
+        <v>338.49</v>
+      </c>
+      <c r="F504" t="n">
+        <v>323.65</v>
+      </c>
+      <c r="G504" t="n">
+        <v>329.68</v>
+      </c>
+      <c r="H504" t="n">
+        <v>348</v>
+      </c>
+      <c r="I504" t="n">
+        <v>364.91</v>
+      </c>
+      <c r="J504" t="n">
+        <v>371.44</v>
+      </c>
+      <c r="K504" t="n">
+        <v>332.52</v>
+      </c>
+      <c r="L504" t="n">
+        <v>348.85</v>
+      </c>
+      <c r="M504" t="n">
+        <v>355.72</v>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>352.39</v>
+      </c>
+      <c r="C505" t="n">
+        <v>347.14</v>
+      </c>
+      <c r="D505" t="n">
+        <v>346.65</v>
+      </c>
+      <c r="E505" t="n">
+        <v>339.22</v>
+      </c>
+      <c r="F505" t="n">
+        <v>322.89</v>
+      </c>
+      <c r="G505" t="n">
+        <v>328.64</v>
+      </c>
+      <c r="H505" t="n">
+        <v>347.95</v>
+      </c>
+      <c r="I505" t="n">
+        <v>364.91</v>
+      </c>
+      <c r="J505" t="n">
+        <v>372.08</v>
+      </c>
+      <c r="K505" t="n">
+        <v>332.4</v>
+      </c>
+      <c r="L505" t="n">
+        <v>349.03</v>
+      </c>
+      <c r="M505" t="n">
+        <v>356.1</v>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>353.21</v>
+      </c>
+      <c r="C506" t="n">
+        <v>347.58</v>
+      </c>
+      <c r="D506" t="n">
+        <v>347.16</v>
+      </c>
+      <c r="E506" t="n">
+        <v>339.53</v>
+      </c>
+      <c r="F506" t="n">
+        <v>323.43</v>
+      </c>
+      <c r="G506" t="n">
+        <v>329.23</v>
+      </c>
+      <c r="H506" t="n">
+        <v>348.74</v>
+      </c>
+      <c r="I506" t="n">
+        <v>365.52</v>
+      </c>
+      <c r="J506" t="n">
+        <v>372.08</v>
+      </c>
+      <c r="K506" t="n">
+        <v>332.83</v>
+      </c>
+      <c r="L506" t="n">
+        <v>349.08</v>
+      </c>
+      <c r="M506" t="n">
+        <v>355.87</v>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>353.28</v>
+      </c>
+      <c r="C507" t="n">
+        <v>347.32</v>
+      </c>
+      <c r="D507" t="n">
+        <v>346.96</v>
+      </c>
+      <c r="E507" t="n">
+        <v>339.1</v>
+      </c>
+      <c r="F507" t="n">
+        <v>324.12</v>
+      </c>
+      <c r="G507" t="n">
+        <v>329.91</v>
+      </c>
+      <c r="H507" t="n">
+        <v>348.78</v>
+      </c>
+      <c r="I507" t="n">
+        <v>366.65</v>
+      </c>
+      <c r="J507" t="n">
+        <v>373.26</v>
+      </c>
+      <c r="K507" t="n">
+        <v>333.16</v>
+      </c>
+      <c r="L507" t="n">
+        <v>349.66</v>
+      </c>
+      <c r="M507" t="n">
+        <v>356.59</v>
+      </c>
+      <c r="N507" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24514,7 +24802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B542"/>
+  <dimension ref="A1:B548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29937,6 +30225,66 @@
       </c>
       <c r="B542" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>-0.57</v>
       </c>
     </row>
   </sheetData>
@@ -30105,28 +30453,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2624275581249933</v>
+        <v>0.2399539985195549</v>
       </c>
       <c r="J2" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="K2" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07077666385279224</v>
+        <v>0.05997373521250327</v>
       </c>
       <c r="M2" t="n">
-        <v>5.987207321733137</v>
+        <v>6.026445531222746</v>
       </c>
       <c r="N2" t="n">
-        <v>55.28298709752688</v>
+        <v>55.88525272915162</v>
       </c>
       <c r="O2" t="n">
-        <v>7.435252994856791</v>
+        <v>7.475643967522237</v>
       </c>
       <c r="P2" t="n">
-        <v>356.6474129938049</v>
+        <v>356.8772950214624</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30183,28 +30531,28 @@
         <v>0.0581</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3333725782324811</v>
+        <v>0.313651698207339</v>
       </c>
       <c r="J3" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="K3" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1169095100762957</v>
+        <v>0.105433761086744</v>
       </c>
       <c r="M3" t="n">
-        <v>5.777751131776986</v>
+        <v>5.809269214492583</v>
       </c>
       <c r="N3" t="n">
-        <v>51.32839886589968</v>
+        <v>51.68808445473707</v>
       </c>
       <c r="O3" t="n">
-        <v>7.164384053489852</v>
+        <v>7.189442569124332</v>
       </c>
       <c r="P3" t="n">
-        <v>347.8410515974356</v>
+        <v>348.0427775938527</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30261,28 +30609,28 @@
         <v>0.043</v>
       </c>
       <c r="I4" t="n">
-        <v>0.321954239880716</v>
+        <v>0.3053693207995372</v>
       </c>
       <c r="J4" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="K4" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1111760657993971</v>
+        <v>0.1021444232162851</v>
       </c>
       <c r="M4" t="n">
-        <v>5.679451189780375</v>
+        <v>5.701919492942625</v>
       </c>
       <c r="N4" t="n">
-        <v>50.66818399887039</v>
+        <v>50.75805555936066</v>
       </c>
       <c r="O4" t="n">
-        <v>7.118158750608924</v>
+        <v>7.124468791380917</v>
       </c>
       <c r="P4" t="n">
-        <v>345.2283397471501</v>
+        <v>345.397959447053</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30339,28 +30687,28 @@
         <v>0.031</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3806346151201563</v>
+        <v>0.3539067736060921</v>
       </c>
       <c r="J5" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="K5" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09951101956842812</v>
+        <v>0.08739969675464765</v>
       </c>
       <c r="M5" t="n">
-        <v>7.330282179778374</v>
+        <v>7.389870432764252</v>
       </c>
       <c r="N5" t="n">
-        <v>80.16160246197445</v>
+        <v>80.9861547876291</v>
       </c>
       <c r="O5" t="n">
-        <v>8.953301204693968</v>
+        <v>8.999230788663501</v>
       </c>
       <c r="P5" t="n">
-        <v>341.2869868080607</v>
+        <v>341.5603741684324</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30417,28 +30765,28 @@
         <v>0.0508</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3257431294984369</v>
+        <v>0.3044327417271163</v>
       </c>
       <c r="J6" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="K6" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08123584076479562</v>
+        <v>0.07229932308783049</v>
       </c>
       <c r="M6" t="n">
-        <v>6.903683030728187</v>
+        <v>6.935319345993042</v>
       </c>
       <c r="N6" t="n">
-        <v>73.37523355219884</v>
+        <v>73.64083541291251</v>
       </c>
       <c r="O6" t="n">
-        <v>8.565934482133216</v>
+        <v>8.581423856966424</v>
       </c>
       <c r="P6" t="n">
-        <v>325.1739115426483</v>
+        <v>325.3919005505642</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30495,28 +30843,28 @@
         <v>0.0368</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1758667388271049</v>
+        <v>0.1639460588513048</v>
       </c>
       <c r="J7" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="K7" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02148579100897841</v>
+        <v>0.01910123570184541</v>
       </c>
       <c r="M7" t="n">
-        <v>7.310985630056646</v>
+        <v>7.283794451230809</v>
       </c>
       <c r="N7" t="n">
-        <v>86.12432126442087</v>
+        <v>85.47262306716817</v>
       </c>
       <c r="O7" t="n">
-        <v>9.280319028159585</v>
+        <v>9.245140510947801</v>
       </c>
       <c r="P7" t="n">
-        <v>330.9325563379709</v>
+        <v>331.05451002559</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30573,28 +30921,28 @@
         <v>0.0357</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2077029119551541</v>
+        <v>0.1945386299692658</v>
       </c>
       <c r="J8" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="K8" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08667931876122648</v>
+        <v>0.07749816750632588</v>
       </c>
       <c r="M8" t="n">
-        <v>3.95744222180222</v>
+        <v>3.993716687685697</v>
       </c>
       <c r="N8" t="n">
-        <v>27.79300946742233</v>
+        <v>27.89650887355621</v>
       </c>
       <c r="O8" t="n">
-        <v>5.271907573869474</v>
+        <v>5.281714577062662</v>
       </c>
       <c r="P8" t="n">
-        <v>348.839386596481</v>
+        <v>348.9740308941787</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30651,28 +30999,28 @@
         <v>0.0322</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1690070713531236</v>
+        <v>0.1601160667660314</v>
       </c>
       <c r="J9" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="K9" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03775295704637582</v>
+        <v>0.03468043940628607</v>
       </c>
       <c r="M9" t="n">
-        <v>4.700489256279901</v>
+        <v>4.698451406736355</v>
       </c>
       <c r="N9" t="n">
-        <v>44.51311281658198</v>
+        <v>44.1894593312111</v>
       </c>
       <c r="O9" t="n">
-        <v>6.67181480682595</v>
+        <v>6.647515274988926</v>
       </c>
       <c r="P9" t="n">
-        <v>365.4244322793136</v>
+        <v>365.5153804726556</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30729,28 +31077,28 @@
         <v>0.0257</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09408641418287345</v>
+        <v>0.06685856905627656</v>
       </c>
       <c r="J10" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="K10" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01023376603978576</v>
+        <v>0.005140568007080626</v>
       </c>
       <c r="M10" t="n">
-        <v>5.670436708994379</v>
+        <v>5.779843566284176</v>
       </c>
       <c r="N10" t="n">
-        <v>52.34721558165526</v>
+        <v>53.57067441462064</v>
       </c>
       <c r="O10" t="n">
-        <v>7.235137564805195</v>
+        <v>7.319199028214811</v>
       </c>
       <c r="P10" t="n">
-        <v>382.4398210958254</v>
+        <v>382.7183211005722</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -30811,28 +31159,28 @@
         <v>0.0708</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5714532584684229</v>
+        <v>0.5466007971016719</v>
       </c>
       <c r="J11" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="K11" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3109777975905869</v>
+        <v>0.2902087910996929</v>
       </c>
       <c r="M11" t="n">
-        <v>5.210994014577602</v>
+        <v>5.290239703435209</v>
       </c>
       <c r="N11" t="n">
-        <v>44.23926084144485</v>
+        <v>45.25045180782668</v>
       </c>
       <c r="O11" t="n">
-        <v>6.651260094256189</v>
+        <v>6.726845606064307</v>
       </c>
       <c r="P11" t="n">
-        <v>329.1459137585637</v>
+        <v>329.4001255821547</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30889,28 +31237,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6159999698077765</v>
+        <v>0.6001815958601396</v>
       </c>
       <c r="J12" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="K12" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3949961608550473</v>
+        <v>0.3843044684170924</v>
       </c>
       <c r="M12" t="n">
-        <v>4.805112977704716</v>
+        <v>4.83638374043981</v>
       </c>
       <c r="N12" t="n">
-        <v>35.53605717830152</v>
+        <v>35.73701396958192</v>
       </c>
       <c r="O12" t="n">
-        <v>5.96121272714718</v>
+        <v>5.978044326498585</v>
       </c>
       <c r="P12" t="n">
-        <v>340.0298543740337</v>
+        <v>340.1916553509778</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30967,28 +31315,28 @@
         <v>0.0422</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5238630095889215</v>
+        <v>0.5149586762517064</v>
       </c>
       <c r="J13" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="K13" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3640395022258722</v>
+        <v>0.3602379233552053</v>
       </c>
       <c r="M13" t="n">
-        <v>4.289865532696271</v>
+        <v>4.289409438506092</v>
       </c>
       <c r="N13" t="n">
-        <v>29.31296154326225</v>
+        <v>29.1632666119604</v>
       </c>
       <c r="O13" t="n">
-        <v>5.414144580934485</v>
+        <v>5.400302455600094</v>
       </c>
       <c r="P13" t="n">
-        <v>346.0398177447493</v>
+        <v>346.130891827444</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31026,7 +31374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N501"/>
+  <dimension ref="A1:N507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67101,6 +67449,438 @@
         </is>
       </c>
     </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>-34.964075296401035,173.64160374784922</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>-34.9644981310383,173.64234249090444</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>-34.964897860194476,173.64310452775166</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>-34.96529494322392,173.64389113264022</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>-34.96565799259765,173.64471239349925</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>-34.96584885779812,173.6456361433344</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>-34.96572784039848,173.64658798953104</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>-34.965521866843076,173.64748262051486</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>-34.96545636422866,173.64838154786983</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>-34.965827622397676,173.64927129904692</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>-34.9657085294444,173.6502096434544</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>-34.96533200544242,173.65101620417732</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>-34.9640718015209,173.6416062523231</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>-34.96449075293862,173.64234777811114</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>-34.96489446571837,173.64310680405583</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>-34.96528929263024,173.6438940246165</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>-34.965649952439506,173.6447156530114</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>-34.965837849331834,173.64563852166364</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>-34.96571683994859,173.64658787295178</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>-34.96553186955661,173.64748305089668</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>-34.96545933984921,173.64838156227322</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>-34.96582221395142,173.64927146926655</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>-34.965705176917034,173.65020878323972</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>-34.965328924895125,173.65101438158496</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>-34.96408290747314,173.64159829366088</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-34.96450053862867,173.64234076560518</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>-34.96489083441829,173.6431092391717</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>-34.965297269938944,173.64388994182636</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>-34.965665776154914,173.64470923801346</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>-34.96586066526593,173.64563359238377</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>-34.96572396319073,173.64658794844163</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>-34.96554133158292,173.64748345801473</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>-34.96546673381544,173.6483815980634</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>-34.96583348154776,173.64927111464232</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>-34.96571249954257,173.6502106621297</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>-34.96533192437539,173.65101615621435</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>-34.96408562571312,173.64159634573625</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>-34.96450263556221,173.64233926292513</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>-34.964884755937625,173.64311331534344</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>-34.96529120386046,173.64389304644808</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>-34.96567227670817,173.64470660266227</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>-34.96586989817305,173.64563159765498</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>-34.96572441402884,173.64658795321947</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>-34.96554133158292,173.64748345801473</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>-34.965460962914975,173.6483815701296</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>-34.96583456323701,173.6492710805984</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>-34.9657109115033,173.65021025465956</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>-34.96532884382811,173.65101433362202</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>-34.96407925726512,173.6416009094452</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>-34.96449921833717,173.64234171173703</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>-34.96488072993088,173.64311601514518</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>-34.96528862785451,173.64389436484896</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>-34.965667657894016,173.6447084751487</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>-34.96586466027382,173.64563272928004</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>-34.9657172907867,173.64658787772962</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>-34.96553583459621,173.64748322149853</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>-34.965460962914975,173.6483815701296</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>-34.965830687183875,173.64927120258912</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>-34.965710470381296,173.65021014147342</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>-34.96533070836989,173.65101543677</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>-34.96407871361712,173.64160129903007</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>-34.96450123760652,173.64234026471183</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>-34.964882308757055,173.64311495639942</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>-34.96529220102405,173.64389253609934</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>-34.965661756075896,173.64471086776993</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>-34.96585862337301,173.64563403352568</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>-34.965716930116216,173.64658787390735</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>-34.965525651653614,173.64748278336202</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>-34.96545032281721,173.64838151862665</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>-34.96582771253843,173.64927129620992</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>-34.965705353365856,173.6502088285142</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>-34.9653248715434,173.65101198343737</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0037/nzd0037.xlsx
+++ b/data/nzd0037/nzd0037.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N507"/>
+  <dimension ref="A1:N512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24786,6 +24786,246 @@
         <v>356.59</v>
       </c>
       <c r="N507" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>353.23</v>
+      </c>
+      <c r="C508" t="n">
+        <v>347.26</v>
+      </c>
+      <c r="D508" t="n">
+        <v>346.66</v>
+      </c>
+      <c r="E508" t="n">
+        <v>338.56</v>
+      </c>
+      <c r="F508" t="n">
+        <v>324.42</v>
+      </c>
+      <c r="G508" t="n">
+        <v>329.79</v>
+      </c>
+      <c r="H508" t="n">
+        <v>348.08</v>
+      </c>
+      <c r="I508" t="n">
+        <v>365.6</v>
+      </c>
+      <c r="J508" t="n">
+        <v>373.26</v>
+      </c>
+      <c r="K508" t="n">
+        <v>333.24</v>
+      </c>
+      <c r="L508" t="n">
+        <v>349.83</v>
+      </c>
+      <c r="M508" t="n">
+        <v>356.34</v>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>353.86</v>
+      </c>
+      <c r="C509" t="n">
+        <v>347.98</v>
+      </c>
+      <c r="D509" t="n">
+        <v>347.33</v>
+      </c>
+      <c r="E509" t="n">
+        <v>339.1</v>
+      </c>
+      <c r="F509" t="n">
+        <v>325.22</v>
+      </c>
+      <c r="G509" t="n">
+        <v>330.56</v>
+      </c>
+      <c r="H509" t="n">
+        <v>349.55</v>
+      </c>
+      <c r="I509" t="n">
+        <v>366.56</v>
+      </c>
+      <c r="J509" t="n">
+        <v>373.26</v>
+      </c>
+      <c r="K509" t="n">
+        <v>333.8</v>
+      </c>
+      <c r="L509" t="n">
+        <v>350.2</v>
+      </c>
+      <c r="M509" t="n">
+        <v>356.43</v>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>354.67</v>
+      </c>
+      <c r="C510" t="n">
+        <v>348.46</v>
+      </c>
+      <c r="D510" t="n">
+        <v>347.92</v>
+      </c>
+      <c r="E510" t="n">
+        <v>339.59</v>
+      </c>
+      <c r="F510" t="n">
+        <v>325.96</v>
+      </c>
+      <c r="G510" t="n">
+        <v>331</v>
+      </c>
+      <c r="H510" t="n">
+        <v>350.11</v>
+      </c>
+      <c r="I510" t="n">
+        <v>367.55</v>
+      </c>
+      <c r="J510" t="n">
+        <v>373.26</v>
+      </c>
+      <c r="K510" t="n">
+        <v>334.2</v>
+      </c>
+      <c r="L510" t="n">
+        <v>350.42</v>
+      </c>
+      <c r="M510" t="n">
+        <v>356.68</v>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>355.38</v>
+      </c>
+      <c r="C511" t="n">
+        <v>348.75</v>
+      </c>
+      <c r="D511" t="n">
+        <v>348.23</v>
+      </c>
+      <c r="E511" t="n">
+        <v>340.27</v>
+      </c>
+      <c r="F511" t="n">
+        <v>326.62</v>
+      </c>
+      <c r="G511" t="n">
+        <v>331.31</v>
+      </c>
+      <c r="H511" t="n">
+        <v>350.35</v>
+      </c>
+      <c r="I511" t="n">
+        <v>369.96</v>
+      </c>
+      <c r="J511" t="n">
+        <v>374.56</v>
+      </c>
+      <c r="K511" t="n">
+        <v>335.21</v>
+      </c>
+      <c r="L511" t="n">
+        <v>351.1</v>
+      </c>
+      <c r="M511" t="n">
+        <v>356.96</v>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>355.9</v>
+      </c>
+      <c r="C512" t="n">
+        <v>349.55</v>
+      </c>
+      <c r="D512" t="n">
+        <v>349.02</v>
+      </c>
+      <c r="E512" t="n">
+        <v>340.27</v>
+      </c>
+      <c r="F512" t="n">
+        <v>327.46</v>
+      </c>
+      <c r="G512" t="n">
+        <v>331.82</v>
+      </c>
+      <c r="H512" t="n">
+        <v>350.29</v>
+      </c>
+      <c r="I512" t="n">
+        <v>371.9</v>
+      </c>
+      <c r="J512" t="n">
+        <v>374.56</v>
+      </c>
+      <c r="K512" t="n">
+        <v>335.59</v>
+      </c>
+      <c r="L512" t="n">
+        <v>351.69</v>
+      </c>
+      <c r="M512" t="n">
+        <v>357.4</v>
+      </c>
+      <c r="N512" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24802,7 +25042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B548"/>
+  <dimension ref="A1:B553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30285,6 +30525,56 @@
       </c>
       <c r="B548" t="n">
         <v>-0.57</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -30453,28 +30743,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2399539985195549</v>
+        <v>0.2246495008419615</v>
       </c>
       <c r="J2" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="K2" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05997373521250327</v>
+        <v>0.05329597689755117</v>
       </c>
       <c r="M2" t="n">
-        <v>6.026445531222746</v>
+        <v>6.041953092844268</v>
       </c>
       <c r="N2" t="n">
-        <v>55.88525272915162</v>
+        <v>56.07591010530287</v>
       </c>
       <c r="O2" t="n">
-        <v>7.475643967522237</v>
+        <v>7.488385013158903</v>
       </c>
       <c r="P2" t="n">
-        <v>356.8772950214624</v>
+        <v>357.034411500535</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30531,28 +30821,28 @@
         <v>0.0581</v>
       </c>
       <c r="I3" t="n">
-        <v>0.313651698207339</v>
+        <v>0.299452348514976</v>
       </c>
       <c r="J3" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="K3" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="L3" t="n">
-        <v>0.105433761086744</v>
+        <v>0.09768033203433135</v>
       </c>
       <c r="M3" t="n">
-        <v>5.809269214492583</v>
+        <v>5.824795248997006</v>
       </c>
       <c r="N3" t="n">
-        <v>51.68808445473707</v>
+        <v>51.81486404313907</v>
       </c>
       <c r="O3" t="n">
-        <v>7.189442569124332</v>
+        <v>7.19825423579489</v>
       </c>
       <c r="P3" t="n">
-        <v>348.0427775938527</v>
+        <v>348.1885522838872</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30609,28 +30899,28 @@
         <v>0.043</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3053693207995372</v>
+        <v>0.2951944942544261</v>
       </c>
       <c r="J4" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="K4" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1021444232162851</v>
+        <v>0.09726606370093804</v>
       </c>
       <c r="M4" t="n">
-        <v>5.701919492942625</v>
+        <v>5.701548332198443</v>
       </c>
       <c r="N4" t="n">
-        <v>50.75805555936066</v>
+        <v>50.58951944897532</v>
       </c>
       <c r="O4" t="n">
-        <v>7.124468791380917</v>
+        <v>7.112630979389786</v>
       </c>
       <c r="P4" t="n">
-        <v>345.397959447053</v>
+        <v>345.502411932268</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30687,28 +30977,28 @@
         <v>0.031</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3539067736060921</v>
+        <v>0.3336787067260346</v>
       </c>
       <c r="J5" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="K5" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08739969675464765</v>
+        <v>0.07875526681918665</v>
       </c>
       <c r="M5" t="n">
-        <v>7.389870432764252</v>
+        <v>7.432021940054974</v>
       </c>
       <c r="N5" t="n">
-        <v>80.9861547876291</v>
+        <v>81.47005646724513</v>
       </c>
       <c r="O5" t="n">
-        <v>8.999230788663501</v>
+        <v>9.02607647138252</v>
       </c>
       <c r="P5" t="n">
-        <v>341.5603741684324</v>
+        <v>341.768049418027</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30765,28 +31055,28 @@
         <v>0.0508</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3044327417271163</v>
+        <v>0.2909988531438174</v>
       </c>
       <c r="J6" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="K6" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07229932308783049</v>
+        <v>0.06722962330037308</v>
       </c>
       <c r="M6" t="n">
-        <v>6.935319345993042</v>
+        <v>6.939026620057657</v>
       </c>
       <c r="N6" t="n">
-        <v>73.64083541291251</v>
+        <v>73.49236806960592</v>
       </c>
       <c r="O6" t="n">
-        <v>8.581423856966424</v>
+        <v>8.572768984966638</v>
       </c>
       <c r="P6" t="n">
-        <v>325.3919005505642</v>
+        <v>325.5298090905652</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30843,28 +31133,28 @@
         <v>0.0368</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1639460588513048</v>
+        <v>0.1559234048185205</v>
       </c>
       <c r="J7" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="K7" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01910123570184541</v>
+        <v>0.01760946904750904</v>
       </c>
       <c r="M7" t="n">
-        <v>7.283794451230809</v>
+        <v>7.252248879126285</v>
       </c>
       <c r="N7" t="n">
-        <v>85.47262306716817</v>
+        <v>84.84107152566804</v>
       </c>
       <c r="O7" t="n">
-        <v>9.245140510947801</v>
+        <v>9.210921317960981</v>
       </c>
       <c r="P7" t="n">
-        <v>331.05451002559</v>
+        <v>331.1368674259819</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30921,28 +31211,28 @@
         <v>0.0357</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1945386299692658</v>
+        <v>0.1865749489902631</v>
       </c>
       <c r="J8" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="K8" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07749816750632588</v>
+        <v>0.07256965310020547</v>
       </c>
       <c r="M8" t="n">
-        <v>3.993716687685697</v>
+        <v>4.00601373767318</v>
       </c>
       <c r="N8" t="n">
-        <v>27.89650887355621</v>
+        <v>27.82777850643783</v>
       </c>
       <c r="O8" t="n">
-        <v>5.281714577062662</v>
+        <v>5.275204119883687</v>
       </c>
       <c r="P8" t="n">
-        <v>348.9740308941787</v>
+        <v>349.0557815244758</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30999,28 +31289,28 @@
         <v>0.0322</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1601160667660314</v>
+        <v>0.1574514909127361</v>
       </c>
       <c r="J9" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="K9" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03468043940628607</v>
+        <v>0.03417084708849405</v>
       </c>
       <c r="M9" t="n">
-        <v>4.698451406736355</v>
+        <v>4.677445466087888</v>
       </c>
       <c r="N9" t="n">
-        <v>44.1894593312111</v>
+        <v>43.83123818496359</v>
       </c>
       <c r="O9" t="n">
-        <v>6.647515274988926</v>
+        <v>6.620516459081088</v>
       </c>
       <c r="P9" t="n">
-        <v>365.5153804726556</v>
+        <v>365.5426882012381</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31077,28 +31367,28 @@
         <v>0.0257</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06685856905627656</v>
+        <v>0.0480828569810843</v>
       </c>
       <c r="J10" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="K10" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005140568007080626</v>
+        <v>0.002663777153664282</v>
       </c>
       <c r="M10" t="n">
-        <v>5.779843566284176</v>
+        <v>5.846727265066243</v>
       </c>
       <c r="N10" t="n">
-        <v>53.57067441462064</v>
+        <v>54.14643294835349</v>
       </c>
       <c r="O10" t="n">
-        <v>7.319199028214811</v>
+        <v>7.358425983072296</v>
       </c>
       <c r="P10" t="n">
-        <v>382.7183211005722</v>
+        <v>382.911085086204</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -31159,28 +31449,28 @@
         <v>0.0708</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5466007971016719</v>
+        <v>0.5295173698088881</v>
       </c>
       <c r="J11" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="K11" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2902087910996929</v>
+        <v>0.2772471844202417</v>
       </c>
       <c r="M11" t="n">
-        <v>5.290239703435209</v>
+        <v>5.336553888696099</v>
       </c>
       <c r="N11" t="n">
-        <v>45.25045180782668</v>
+        <v>45.7223652789659</v>
       </c>
       <c r="O11" t="n">
-        <v>6.726845606064307</v>
+        <v>6.761831503295975</v>
       </c>
       <c r="P11" t="n">
-        <v>329.4001255821547</v>
+        <v>329.5755087178167</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31237,28 +31527,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6001815958601396</v>
+        <v>0.5900908349220324</v>
       </c>
       <c r="J12" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="K12" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3843044684170924</v>
+        <v>0.3788746806681006</v>
       </c>
       <c r="M12" t="n">
-        <v>4.83638374043981</v>
+        <v>4.845209369252868</v>
       </c>
       <c r="N12" t="n">
-        <v>35.73701396958192</v>
+        <v>35.70812182826083</v>
       </c>
       <c r="O12" t="n">
-        <v>5.978044326498585</v>
+        <v>5.97562731671419</v>
       </c>
       <c r="P12" t="n">
-        <v>340.1916553509778</v>
+        <v>340.2952469842564</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31315,28 +31605,28 @@
         <v>0.0422</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5149586762517064</v>
+        <v>0.5092017434397826</v>
       </c>
       <c r="J13" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="K13" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3602379233552053</v>
+        <v>0.3588176411486413</v>
       </c>
       <c r="M13" t="n">
-        <v>4.289409438506092</v>
+        <v>4.279845629525996</v>
       </c>
       <c r="N13" t="n">
-        <v>29.1632666119604</v>
+        <v>28.98232093660196</v>
       </c>
       <c r="O13" t="n">
-        <v>5.400302455600094</v>
+        <v>5.38352309706218</v>
       </c>
       <c r="P13" t="n">
-        <v>346.130891827444</v>
+        <v>346.1899927929942</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31374,7 +31664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N507"/>
+  <dimension ref="A1:N512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67881,6 +68171,366 @@
         </is>
       </c>
     </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>-34.964079101937116,173.6416010207552</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>-34.96450170359174,173.64233993078295</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>-34.96488467699631,173.64311336828072</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>-34.965296688260175,173.64389023952984</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>-34.965659190068,173.64471190803994</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>-34.96585968870844,173.6456338033647</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>-34.96572324184976,173.64658794079708</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>-34.96553511367991,173.64748319048002</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>-34.96545032281721,173.64838151862665</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>-34.96582699141227,173.64927131890587</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>-34.96570385355097,173.65020844368135</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>-34.965326898219274,173.65101318251115</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>-34.964074209105,173.6416045270189</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>-34.96449611176894,173.6423439379295</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>-34.96487938792861,173.64311691507905</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>-34.96529220102405,173.64389253609934</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>-34.96565234738025,173.64471468209297</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>-34.96585285280604,173.6456352802309</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>-34.96570998720931,173.64658780032866</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>-34.965526462684444,173.64748281825786</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>-34.96545032281721,173.64838151862665</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>-34.9658219435291,173.64927147777752</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>-34.965700589248016,173.65020760610403</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>-34.96532616861595,173.65101275084456</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-34.96406791832071,173.64160903507164</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-34.96449238388699,173.64234660936026</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>-34.96487473039129,173.64312003837864</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>-34.96528812927271,173.64389462002333</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>-34.96564601789401,173.6447172480916</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>-34.96584894657607,173.64563612415432</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>-34.96570493782245,173.6465877468169</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>-34.965517541345335,173.64748243440386</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>-34.96545032281721,173.64838151862665</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>-34.96581833789827,173.64927159125725</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>-34.96569864831111,173.6502071080851</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>-34.96532414194007,173.6510115517708</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-34.964062404176296,173.6416129865741</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-34.96449013162495,173.64234822334956</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>-34.96487228321061,173.64312167943422</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>-34.96528247867896,173.64389751199914</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>-34.96564037267651,173.64471953668465</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>-34.9658461944595,173.64563671873668</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>-34.96570277379952,173.64658772388327</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>-34.96549582374198,173.64748149997178</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>-34.96543860067562,173.64838146188612</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>-34.965809233680396,173.64927187779355</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>-34.965692649051576,173.6502055687541</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>-34.96532187206308,173.6510102088083</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-34.96405836564793,173.6416158806319</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-34.96448391848818,173.64235267573335</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-34.964866046846915,173.6431258614787</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-34.96528247867896,173.64389751199914</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>-34.965633187854166,173.644722449439</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>-34.96584166678385,173.64563769692055</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>-34.96570331480527,173.64658772961667</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>-34.9654783415218,173.64748074777378</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>-34.96543860067562,173.64838146188612</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>-34.96580580833109,173.64927198559928</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>-34.96568744381166,173.65020423315826</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>-34.96531830511346,173.65100809843872</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0037/nzd0037.xlsx
+++ b/data/nzd0037/nzd0037.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N512"/>
+  <dimension ref="A1:N516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25026,6 +25026,198 @@
         <v>357.4</v>
       </c>
       <c r="N512" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>357.22</v>
+      </c>
+      <c r="C513" t="n">
+        <v>351.3</v>
+      </c>
+      <c r="D513" t="n">
+        <v>349.37</v>
+      </c>
+      <c r="E513" t="n">
+        <v>340.47</v>
+      </c>
+      <c r="F513" t="n">
+        <v>327.96</v>
+      </c>
+      <c r="G513" t="n">
+        <v>331.82</v>
+      </c>
+      <c r="H513" t="n">
+        <v>350.29</v>
+      </c>
+      <c r="I513" t="n">
+        <v>371.9</v>
+      </c>
+      <c r="J513" t="n">
+        <v>374.56</v>
+      </c>
+      <c r="K513" t="n">
+        <v>335.59</v>
+      </c>
+      <c r="L513" t="n">
+        <v>351.69</v>
+      </c>
+      <c r="M513" t="n">
+        <v>357.4</v>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>358</v>
+      </c>
+      <c r="C514" t="n">
+        <v>352.03</v>
+      </c>
+      <c r="D514" t="n">
+        <v>349.79</v>
+      </c>
+      <c r="E514" t="n">
+        <v>340.78</v>
+      </c>
+      <c r="F514" t="n">
+        <v>328.55</v>
+      </c>
+      <c r="G514" t="n">
+        <v>332.22</v>
+      </c>
+      <c r="H514" t="n">
+        <v>350.31</v>
+      </c>
+      <c r="I514" t="n">
+        <v>371.9</v>
+      </c>
+      <c r="J514" t="n">
+        <v>374.56</v>
+      </c>
+      <c r="K514" t="n">
+        <v>336.28</v>
+      </c>
+      <c r="L514" t="n">
+        <v>351.98</v>
+      </c>
+      <c r="M514" t="n">
+        <v>357.67</v>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:17:33+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>358</v>
+      </c>
+      <c r="C515" t="n">
+        <v>352.03</v>
+      </c>
+      <c r="D515" t="n">
+        <v>349.79</v>
+      </c>
+      <c r="E515" t="n">
+        <v>340.78</v>
+      </c>
+      <c r="F515" t="n">
+        <v>328.78</v>
+      </c>
+      <c r="G515" t="n">
+        <v>332.37</v>
+      </c>
+      <c r="H515" t="n">
+        <v>350.18</v>
+      </c>
+      <c r="I515" t="n">
+        <v>371.03</v>
+      </c>
+      <c r="J515" t="n">
+        <v>374.82</v>
+      </c>
+      <c r="K515" t="n">
+        <v>336.39</v>
+      </c>
+      <c r="L515" t="n">
+        <v>351.94</v>
+      </c>
+      <c r="M515" t="n">
+        <v>357.62</v>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>357.61</v>
+      </c>
+      <c r="C516" t="n">
+        <v>351.5</v>
+      </c>
+      <c r="D516" t="n">
+        <v>349.71</v>
+      </c>
+      <c r="E516" t="n">
+        <v>340.33</v>
+      </c>
+      <c r="F516" t="n">
+        <v>328.9</v>
+      </c>
+      <c r="G516" t="n">
+        <v>331.89</v>
+      </c>
+      <c r="H516" t="n">
+        <v>350.27</v>
+      </c>
+      <c r="I516" t="n">
+        <v>371.54</v>
+      </c>
+      <c r="J516" t="n">
+        <v>376.27</v>
+      </c>
+      <c r="K516" t="n">
+        <v>337.02</v>
+      </c>
+      <c r="L516" t="n">
+        <v>352.62</v>
+      </c>
+      <c r="M516" t="n">
+        <v>357.87</v>
+      </c>
+      <c r="N516" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25042,7 +25234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B553"/>
+  <dimension ref="A1:B557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30575,6 +30767,46 @@
       </c>
       <c r="B553" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>
@@ -30743,28 +30975,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2246495008419615</v>
+        <v>0.2171822267920485</v>
       </c>
       <c r="J2" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K2" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05329597689755117</v>
+        <v>0.05054148498608357</v>
       </c>
       <c r="M2" t="n">
-        <v>6.041953092844268</v>
+        <v>6.031203907729767</v>
       </c>
       <c r="N2" t="n">
-        <v>56.07591010530287</v>
+        <v>55.86406080714607</v>
       </c>
       <c r="O2" t="n">
-        <v>7.488385013158903</v>
+        <v>7.47422643536748</v>
       </c>
       <c r="P2" t="n">
-        <v>357.034411500535</v>
+        <v>357.1114348071324</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30821,28 +31053,28 @@
         <v>0.0581</v>
       </c>
       <c r="I3" t="n">
-        <v>0.299452348514976</v>
+        <v>0.2931164145965685</v>
       </c>
       <c r="J3" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K3" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09768033203433135</v>
+        <v>0.09504614666025701</v>
       </c>
       <c r="M3" t="n">
-        <v>5.824795248997006</v>
+        <v>5.811914754773954</v>
       </c>
       <c r="N3" t="n">
-        <v>51.81486404313907</v>
+        <v>51.57368237553651</v>
       </c>
       <c r="O3" t="n">
-        <v>7.19825423579489</v>
+        <v>7.181481906649665</v>
       </c>
       <c r="P3" t="n">
-        <v>348.1885522838872</v>
+        <v>348.2539073464489</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30899,28 +31131,28 @@
         <v>0.043</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2951944942544261</v>
+        <v>0.2898931146486195</v>
       </c>
       <c r="J4" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K4" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09726606370093804</v>
+        <v>0.09527941749848368</v>
       </c>
       <c r="M4" t="n">
-        <v>5.701548332198443</v>
+        <v>5.685741041293272</v>
       </c>
       <c r="N4" t="n">
-        <v>50.58951944897532</v>
+        <v>50.30916633726162</v>
       </c>
       <c r="O4" t="n">
-        <v>7.112630979389786</v>
+        <v>7.092895483317205</v>
       </c>
       <c r="P4" t="n">
-        <v>345.502411932268</v>
+        <v>345.5570936280803</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30977,28 +31209,28 @@
         <v>0.031</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3336787067260346</v>
+        <v>0.319580008304105</v>
       </c>
       <c r="J5" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K5" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07875526681918665</v>
+        <v>0.07311090646368057</v>
       </c>
       <c r="M5" t="n">
-        <v>7.432021940054974</v>
+        <v>7.453586231762541</v>
       </c>
       <c r="N5" t="n">
-        <v>81.47005646724513</v>
+        <v>81.63205950544939</v>
       </c>
       <c r="O5" t="n">
-        <v>9.02607647138252</v>
+        <v>9.035046181699869</v>
       </c>
       <c r="P5" t="n">
-        <v>341.768049418027</v>
+        <v>341.9134767408053</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31055,28 +31287,28 @@
         <v>0.0508</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2909988531438174</v>
+        <v>0.2842766335253167</v>
       </c>
       <c r="J6" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K6" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06722962330037308</v>
+        <v>0.06515411642567015</v>
       </c>
       <c r="M6" t="n">
-        <v>6.939026620057657</v>
+        <v>6.921304909141488</v>
       </c>
       <c r="N6" t="n">
-        <v>73.49236806960592</v>
+        <v>73.10320717746656</v>
       </c>
       <c r="O6" t="n">
-        <v>8.572768984966638</v>
+        <v>8.550041355307386</v>
       </c>
       <c r="P6" t="n">
-        <v>325.5298090905652</v>
+        <v>325.5991425908945</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31133,28 +31365,28 @@
         <v>0.0368</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1559234048185205</v>
+        <v>0.1513876001809453</v>
       </c>
       <c r="J7" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K7" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01760946904750904</v>
+        <v>0.01685803300200828</v>
       </c>
       <c r="M7" t="n">
-        <v>7.252248879126285</v>
+        <v>7.218283079432305</v>
       </c>
       <c r="N7" t="n">
-        <v>84.84107152566804</v>
+        <v>84.26474038877673</v>
       </c>
       <c r="O7" t="n">
-        <v>9.210921317960981</v>
+        <v>9.179582800366077</v>
       </c>
       <c r="P7" t="n">
-        <v>331.1368674259819</v>
+        <v>331.1836542587496</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31211,28 +31443,28 @@
         <v>0.0357</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1865749489902631</v>
+        <v>0.1812640705067871</v>
       </c>
       <c r="J8" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K8" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07256965310020547</v>
+        <v>0.06952216426656388</v>
       </c>
       <c r="M8" t="n">
-        <v>4.00601373767318</v>
+        <v>4.009305976140625</v>
       </c>
       <c r="N8" t="n">
-        <v>27.82777850643783</v>
+        <v>27.7243995149734</v>
       </c>
       <c r="O8" t="n">
-        <v>5.275204119883687</v>
+        <v>5.265396425244105</v>
       </c>
       <c r="P8" t="n">
-        <v>349.0557815244758</v>
+        <v>349.110562421177</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31289,28 +31521,28 @@
         <v>0.0322</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1574514909127361</v>
+        <v>0.159900963185711</v>
       </c>
       <c r="J9" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K9" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03417084708849405</v>
+        <v>0.03572022600812141</v>
       </c>
       <c r="M9" t="n">
-        <v>4.677445466087888</v>
+        <v>4.653208689140465</v>
       </c>
       <c r="N9" t="n">
-        <v>43.83123818496359</v>
+        <v>43.51579895137646</v>
       </c>
       <c r="O9" t="n">
-        <v>6.620516459081088</v>
+        <v>6.596650585818265</v>
       </c>
       <c r="P9" t="n">
-        <v>365.5426882012381</v>
+        <v>365.5174251503196</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31367,28 +31599,28 @@
         <v>0.0257</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0480828569810843</v>
+        <v>0.03546152472576781</v>
       </c>
       <c r="J10" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K10" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L10" t="n">
-        <v>0.002663777153664282</v>
+        <v>0.001456145126093156</v>
       </c>
       <c r="M10" t="n">
-        <v>5.846727265066243</v>
+        <v>5.886249450724188</v>
       </c>
       <c r="N10" t="n">
-        <v>54.14643294835349</v>
+        <v>54.3667328261286</v>
       </c>
       <c r="O10" t="n">
-        <v>7.358425983072296</v>
+        <v>7.37338001367952</v>
       </c>
       <c r="P10" t="n">
-        <v>382.911085086204</v>
+        <v>383.0412587190364</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -31449,28 +31681,28 @@
         <v>0.0708</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5295173698088881</v>
+        <v>0.5190139380528561</v>
       </c>
       <c r="J11" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K11" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2772471844202417</v>
+        <v>0.2704588240946744</v>
       </c>
       <c r="M11" t="n">
-        <v>5.336553888696099</v>
+        <v>5.354660228881242</v>
       </c>
       <c r="N11" t="n">
-        <v>45.7223652789659</v>
+        <v>45.81024747551179</v>
       </c>
       <c r="O11" t="n">
-        <v>6.761831503295975</v>
+        <v>6.768326785514407</v>
       </c>
       <c r="P11" t="n">
-        <v>329.5755087178167</v>
+        <v>329.6838413656049</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31527,28 +31759,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5900908349220324</v>
+        <v>0.5842371959936931</v>
       </c>
       <c r="J12" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K12" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3788746806681006</v>
+        <v>0.3769535541493723</v>
       </c>
       <c r="M12" t="n">
-        <v>4.845209369252868</v>
+        <v>4.839782518262706</v>
       </c>
       <c r="N12" t="n">
-        <v>35.70812182826083</v>
+        <v>35.56861296084813</v>
       </c>
       <c r="O12" t="n">
-        <v>5.97562731671419</v>
+        <v>5.963942736214704</v>
       </c>
       <c r="P12" t="n">
-        <v>340.2952469842564</v>
+        <v>340.3556204108705</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31605,28 +31837,28 @@
         <v>0.0422</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5092017434397826</v>
+        <v>0.5059404484614815</v>
       </c>
       <c r="J13" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="K13" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3588176411486413</v>
+        <v>0.3591201908941463</v>
       </c>
       <c r="M13" t="n">
-        <v>4.279845629525996</v>
+        <v>4.264944687903935</v>
       </c>
       <c r="N13" t="n">
-        <v>28.98232093660196</v>
+        <v>28.7999352627649</v>
       </c>
       <c r="O13" t="n">
-        <v>5.38352309706218</v>
+        <v>5.366557114460341</v>
       </c>
       <c r="P13" t="n">
-        <v>346.1899927929942</v>
+        <v>346.2236299704402</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31664,7 +31896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N512"/>
+  <dimension ref="A1:N516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68531,6 +68763,294 @@
         </is>
       </c>
     </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-34.964048113998665,173.64162322708506</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-34.96447032725094,173.64236241532058</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>-34.964863283900925,173.643127714283</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-34.96528081673961,173.64389836258016</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-34.965628911174164,173.64472418322111</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>-34.96584166678385,173.64563769692055</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>-34.96570331480527,173.64658772961667</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>-34.9654783415218,173.64748074777378</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>-34.96543860067562,173.64838146188612</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>-34.96580580833109,173.64927198559928</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>-34.96568744381166,173.65020423315826</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>-34.96531830511346,173.65100809843872</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-34.96404205620572,173.64162756817018</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-34.96446465776319,173.64236647811887</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-34.964859968365694,173.64312993764798</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-34.965278240733596,173.64389968098072</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>-34.96562386469172,173.64472622908377</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>-34.96583811566568,173.64563846412346</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>-34.96570313447001,173.64658772770554</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>-34.9654783415218,173.64748074777378</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>-34.96543860067562,173.64838146188612</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>-34.965799588617884,173.6492721813518</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>-34.9656848853039,173.650203576679</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>-34.96531611630347,173.65100680343932</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:17:33+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-34.96404205620572,173.64162756817018</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-34.96446465776319,173.64236647811887</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-34.964859968365694,173.64312993764798</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-34.965278240733596,173.64389968098072</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>-34.96562189741891,173.6447270266234</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>-34.96583678399638,173.64563875182452</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>-34.9657043066491,173.64658774012793</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>-34.965486181486526,173.64748108509963</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>-34.965436256247294,173.64838145053804</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>-34.9657985970694,173.64927221255869</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>-34.96568523820152,173.65020366722786</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>-34.965316521638655,173.65100704325403</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-34.964045085102214,173.64162539762768</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-34.96446877396666,173.64236352841604</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>-34.96486059989621,173.6431295141499</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>-34.96528198009716,173.64389776717343</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>-34.96562087101569,173.644727442731</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>-34.96584104533818,173.64563783118103</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>-34.9657034951405,173.6465877315278</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>-34.96548158564513,173.6474808873569</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>-34.965423181550875,173.64838138725062</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>-34.96579291820082,173.6492723912892</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>-34.965679238941924,173.65020212789733</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>-34.965314494962705,173.65100584418056</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
